--- a/PC_2014/E__ScanF20_PC_032.xlsx
+++ b/PC_2014/E__ScanF20_PC_032.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +45,19 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -59,8 +70,32 @@
         <bgColor rgb="001F497D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B365D"/>
+        <bgColor rgb="001B365D"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -82,11 +117,53 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="medium">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001B365D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -99,6 +176,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -465,11 +560,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X87"/>
+  <dimension ref="A1:Y89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -522,117 +617,122 @@
           <t>PS_No</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>PS_Name</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Chennamaneni Vidya Sagar Rao</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Ponnam Prabhakar</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Burla Ravi</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Byagari Laxman</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Vinod Kumar Boinapally</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Dr. Dharmaiah Vendavetla</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Lenkala Prabhakar Reddy</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Meesala Raji Reddy</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Ranaveni Lakshman</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Reddi Malla Srinivas</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Shaik Mohmood</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Uppuleti Laxman</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Kandem Prabhakar</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>Pulikota Ramesh</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>Mallesh Yadav Barla</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>Mommed Amjad Mohiuddin</t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>Srinvas Reddy Lingampally</t>
         </is>
       </c>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>Total_Valid_Votes</t>
         </is>
       </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <t>Rejected_Votes</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
+      <c r="V5" s="3" t="inlineStr">
         <is>
           <t>NOTA</t>
         </is>
       </c>
-      <c r="V5" s="3" t="inlineStr">
+      <c r="W5" s="3" t="inlineStr">
         <is>
           <t>Total_Votes</t>
         </is>
       </c>
-      <c r="W5" s="3" t="inlineStr">
+      <c r="X5" s="3" t="inlineStr">
         <is>
           <t>Tendered_Votes</t>
         </is>
       </c>
-      <c r="X5" s="3" t="inlineStr">
+      <c r="Y5" s="3" t="inlineStr">
         <is>
           <t>Checksum_Diff</t>
         </is>
@@ -642,8 +742,10 @@
       <c r="A6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>0</v>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>PANDILLA</t>
+        </is>
       </c>
       <c r="C6" s="4" t="n">
         <v>0</v>
@@ -655,11 +757,11 @@
         <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="G6" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H6" s="4" t="n">
         <v>0</v>
       </c>
@@ -676,10 +778,10 @@
         <v>0</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O6" s="4" t="n">
         <v>0</v>
@@ -694,10 +796,10 @@
         <v>0</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U6" s="4" t="n">
         <v>0</v>
@@ -706,34 +808,40 @@
         <v>0</v>
       </c>
       <c r="W6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="X6" s="4" t="n">
-        <v>62</v>
+      <c r="Y6" s="4">
+        <f>SUM(C6:S6)-T6</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>0</v>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>PANDILLA</t>
+        </is>
       </c>
       <c r="C7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4" t="n">
         <v>2001</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="E7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="n">
         <v>866</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H7" s="4" t="n">
         <v>0</v>
       </c>
@@ -750,11 +858,11 @@
         <v>0</v>
       </c>
       <c r="M7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="N7" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O7" s="4" t="n">
         <v>0</v>
       </c>
@@ -780,28 +888,34 @@
         <v>0</v>
       </c>
       <c r="W7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="4" t="n">
         <v>99</v>
       </c>
-      <c r="X7" s="4" t="n">
-        <v>2940</v>
+      <c r="Y7" s="4">
+        <f>SUM(C7:S7)-T7</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="4" t="n">
-        <v>0</v>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>BANJERUPALLE</t>
+        </is>
       </c>
       <c r="C8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4" t="n">
         <v>901</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="E8" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="E8" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F8" s="4" t="n">
         <v>0</v>
       </c>
@@ -809,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>0</v>
@@ -827,11 +941,11 @@
         <v>0</v>
       </c>
       <c r="N8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="O8" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P8" s="4" t="n">
         <v>0</v>
       </c>
@@ -845,27 +959,33 @@
         <v>0</v>
       </c>
       <c r="T8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="U8" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="W8" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="X8" s="4" t="n">
-        <v>926</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="4">
+        <f>SUM(C8:S8)-T8</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="4" t="n">
-        <v>0</v>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>POTLAPALLE</t>
+        </is>
       </c>
       <c r="C9" s="4" t="n">
         <v>0</v>
@@ -877,17 +997,17 @@
         <v>0</v>
       </c>
       <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="I9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="I9" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J9" s="4" t="n">
         <v>0</v>
       </c>
@@ -898,11 +1018,11 @@
         <v>0</v>
       </c>
       <c r="M9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="N9" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O9" s="4" t="n">
         <v>0</v>
       </c>
@@ -925,30 +1045,36 @@
         <v>0</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W9" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="X9" s="4" t="n">
         <v>82</v>
       </c>
-      <c r="X9" s="4" t="n">
-        <v>24</v>
+      <c r="Y9" s="4">
+        <f>SUM(C9:S9)-T9</f>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="4" t="n">
-        <v>0</v>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>POTLAPALLI</t>
+        </is>
       </c>
       <c r="C10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="D10" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="E10" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>0</v>
@@ -972,11 +1098,11 @@
         <v>0</v>
       </c>
       <c r="M10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="N10" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O10" s="4" t="n">
         <v>0</v>
       </c>
@@ -990,37 +1116,43 @@
         <v>0</v>
       </c>
       <c r="S10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="T10" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="W10" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="X10" s="4" t="n">
-        <v>45</v>
+        <v>9</v>
+      </c>
+      <c r="Y10" s="4">
+        <f>SUM(C10:S10)-T10</f>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="4" t="n">
-        <v>0</v>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>HUSNABAD</t>
+        </is>
       </c>
       <c r="C11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="D11" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
       </c>
@@ -1070,31 +1202,37 @@
         <v>0</v>
       </c>
       <c r="U11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V11" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="W11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>61</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="4">
+        <f>SUM(C11:S11)-T11</f>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="4" t="n">
-        <v>0</v>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>HUSNABAD</t>
+        </is>
       </c>
       <c r="C12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="4" t="n">
         <v>79</v>
       </c>
-      <c r="D12" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E12" s="4" t="n">
         <v>0</v>
       </c>
@@ -1120,13 +1258,13 @@
         <v>0</v>
       </c>
       <c r="M12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4" t="n">
         <v>82</v>
       </c>
-      <c r="N12" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="O12" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P12" s="4" t="n">
         <v>0</v>
@@ -1138,52 +1276,58 @@
         <v>0</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="T12" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="U12" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="U12" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="W12" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="X12" s="4" t="n">
-        <v>161</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="4">
+        <f>SUM(C12:S12)-T12</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="4" t="n">
-        <v>0</v>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>HUSNABAD</t>
+        </is>
       </c>
       <c r="C13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="4" t="n">
         <v>726</v>
       </c>
-      <c r="D13" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="G13" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="I13" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J13" s="4" t="n">
         <v>0</v>
       </c>
@@ -1218,40 +1362,46 @@
         <v>0</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="W13" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="W13" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="X13" s="4" t="n">
-        <v>758</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="4">
+        <f>SUM(C13:S13)-T13</f>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="4" t="n">
-        <v>0</v>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>HUSNABAD</t>
+        </is>
       </c>
       <c r="C14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="D14" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="G14" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H14" s="4" t="n">
         <v>0</v>
       </c>
@@ -1277,20 +1427,20 @@
         <v>0</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="T14" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U14" s="4" t="n">
         <v>0</v>
       </c>
@@ -1301,22 +1451,30 @@
         <v>0</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="4">
+        <f>SUM(C14:S14)-T14</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="4" t="n">
-        <v>0</v>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Mandala Parishad Primary School
+(New Building) Arepally H/o
+Husnabad</t>
+        </is>
       </c>
       <c r="C15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="D15" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E15" s="4" t="n">
         <v>0</v>
       </c>
@@ -1345,11 +1503,11 @@
         <v>0</v>
       </c>
       <c r="N15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="O15" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P15" s="4" t="n">
         <v>0</v>
       </c>
@@ -1369,37 +1527,43 @@
         <v>0</v>
       </c>
       <c r="V15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="W15" s="4" t="n">
+      <c r="X15" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="X15" s="4" t="n">
-        <v>70</v>
+      <c r="Y15" s="4">
+        <f>SUM(C15:S15)-T15</f>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="4" t="n">
-        <v>0</v>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>HUSNABAD</t>
+        </is>
       </c>
       <c r="C16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="E16" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="n">
         <v>89</v>
       </c>
-      <c r="G16" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H16" s="4" t="n">
         <v>0</v>
       </c>
@@ -1416,11 +1580,11 @@
         <v>0</v>
       </c>
       <c r="M16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="N16" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O16" s="4" t="n">
         <v>0</v>
       </c>
@@ -1443,36 +1607,42 @@
         <v>0</v>
       </c>
       <c r="V16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="4" t="n">
         <v>98</v>
       </c>
-      <c r="W16" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="X16" s="4" t="n">
-        <v>160</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="4">
+        <f>SUM(C16:S16)-T16</f>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="4" t="n">
-        <v>0</v>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>HUSNABAD</t>
+        </is>
       </c>
       <c r="C17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H17" s="4" t="n">
         <v>0</v>
@@ -1481,11 +1651,11 @@
         <v>0</v>
       </c>
       <c r="J17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="K17" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="L17" s="4" t="n">
         <v>0</v>
       </c>
@@ -1505,11 +1675,11 @@
         <v>0</v>
       </c>
       <c r="R17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="S17" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="T17" s="4" t="n">
         <v>0</v>
       </c>
@@ -1517,21 +1687,27 @@
         <v>0</v>
       </c>
       <c r="V17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="4" t="n">
         <v>647</v>
       </c>
-      <c r="W17" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="X17" s="4" t="n">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="4">
+        <f>SUM(C17:S17)-T17</f>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="4" t="n">
-        <v>0</v>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>HUSNABAD</t>
+        </is>
       </c>
       <c r="C18" s="4" t="n">
         <v>0</v>
@@ -1555,26 +1731,26 @@
         <v>0</v>
       </c>
       <c r="J18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K18" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="N18" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="P18" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
@@ -1585,11 +1761,11 @@
         <v>0</v>
       </c>
       <c r="T18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="U18" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V18" s="4" t="n">
         <v>0</v>
       </c>
@@ -1597,31 +1773,37 @@
         <v>0</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>48</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="4">
+        <f>SUM(C18:S18)-T18</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="4" t="n">
-        <v>0</v>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>HUSNABAD</t>
+        </is>
       </c>
       <c r="C19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D19" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G19" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H19" s="4" t="n">
         <v>0</v>
       </c>
@@ -1632,11 +1814,11 @@
         <v>0</v>
       </c>
       <c r="K19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L19" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" s="4" t="n">
         <v>0</v>
       </c>
@@ -1650,20 +1832,20 @@
         <v>0</v>
       </c>
       <c r="Q19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="R19" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="T19" s="4" t="n">
+      <c r="U19" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="U19" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V19" s="4" t="n">
         <v>0</v>
       </c>
@@ -1671,30 +1853,36 @@
         <v>0</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="4">
+        <f>SUM(C19:S19)-T19</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="4" t="n">
-        <v>0</v>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>HUSNABAD,</t>
+        </is>
       </c>
       <c r="C20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="4" t="n">
         <v>799</v>
       </c>
-      <c r="D20" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H20" s="4" t="n">
         <v>0</v>
@@ -1718,11 +1906,11 @@
         <v>0</v>
       </c>
       <c r="O20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="P20" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
@@ -1745,15 +1933,21 @@
         <v>0</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>810</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="4">
+        <f>SUM(C20:S20)-T20</f>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="4" t="n">
-        <v>0</v>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>HUSNABAD</t>
+        </is>
       </c>
       <c r="C21" s="4" t="n">
         <v>0</v>
@@ -1786,11 +1980,11 @@
         <v>0</v>
       </c>
       <c r="M21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="4" t="n">
         <v>92</v>
       </c>
-      <c r="N21" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O21" s="4" t="n">
         <v>0</v>
       </c>
@@ -1804,30 +1998,36 @@
         <v>0</v>
       </c>
       <c r="S21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="4" t="n">
         <v>262</v>
       </c>
-      <c r="T21" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="W21" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="X21" s="4" t="n">
-        <v>-170</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="4">
+        <f>SUM(C21:S21)-T21</f>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="4" t="n">
-        <v>0</v>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>HUSNABAD</t>
+        </is>
       </c>
       <c r="C22" s="4" t="n">
         <v>0</v>
@@ -1845,79 +2045,85 @@
         <v>0</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="L22" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="O22" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q22" s="4" t="n">
+      <c r="R22" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="R22" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="T22" s="4" t="n">
         <v>9</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="4">
+        <f>SUM(C22:S22)-T22</f>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="4" t="n">
-        <v>0</v>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>HUSNABAD</t>
+        </is>
       </c>
       <c r="C23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="G23" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H23" s="4" t="n">
         <v>0</v>
       </c>
@@ -1934,10 +2140,10 @@
         <v>0</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O23" s="4" t="n">
         <v>0</v>
@@ -1961,37 +2167,43 @@
         <v>0</v>
       </c>
       <c r="V23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" s="4" t="n">
         <v>92</v>
       </c>
-      <c r="W23" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="X23" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="4">
+        <f>SUM(C23:S23)-T23</f>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="4" t="n">
-        <v>0</v>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>HUSNABAD</t>
+        </is>
       </c>
       <c r="C24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="4" t="n">
         <v>99</v>
       </c>
-      <c r="D24" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="G24" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H24" s="4" t="n">
         <v>0</v>
       </c>
@@ -2008,11 +2220,11 @@
         <v>0</v>
       </c>
       <c r="M24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N24" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O24" s="4" t="n">
         <v>0</v>
       </c>
@@ -2026,39 +2238,45 @@
         <v>0</v>
       </c>
       <c r="S24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="4" t="n">
         <v>162</v>
       </c>
-      <c r="T24" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="4">
+        <f>SUM(C24:S24)-T24</f>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="4" t="n">
-        <v>0</v>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>HUSNABAD</t>
+        </is>
       </c>
       <c r="C25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D25" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="E25" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F25" s="4" t="n">
         <v>0</v>
@@ -2100,46 +2318,52 @@
         <v>0</v>
       </c>
       <c r="S25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="4" t="n">
         <v>92</v>
       </c>
-      <c r="T25" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="W25" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="X25" s="4" t="n">
-        <v>-77</v>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="4">
+        <f>SUM(C25:S25)-T25</f>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B26" s="4" t="n">
-        <v>0</v>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>HUSNABAD</t>
+        </is>
       </c>
       <c r="C26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="D26" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="G26" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H26" s="4" t="n">
         <v>0</v>
       </c>
@@ -2156,11 +2380,11 @@
         <v>0</v>
       </c>
       <c r="M26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="N26" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O26" s="4" t="n">
         <v>0</v>
       </c>
@@ -2177,43 +2401,49 @@
         <v>0</v>
       </c>
       <c r="T26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="U26" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="4" t="n">
         <v>681</v>
       </c>
-      <c r="W26" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="X26" s="4" t="n">
-        <v>60</v>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="4">
+        <f>SUM(C26:S26)-T26</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B27" s="4" t="n">
-        <v>0</v>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>HUSNABAD</t>
+        </is>
       </c>
       <c r="C27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="4" t="n">
         <v>99</v>
       </c>
-      <c r="D27" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E27" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="n">
         <v>99</v>
       </c>
-      <c r="G27" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H27" s="4" t="n">
         <v>0</v>
       </c>
@@ -2230,48 +2460,55 @@
         <v>0</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O27" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="T27" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U27" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="W27" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="X27" s="4" t="n">
-        <v>150</v>
+        <v>9</v>
+      </c>
+      <c r="Y27" s="4">
+        <f>SUM(C27:S27)-T27</f>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B28" s="4" t="n">
-        <v>0</v>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Mandal Parishad Upper Primay
+School Madadha</t>
+        </is>
       </c>
       <c r="C28" s="4" t="n">
         <v>0</v>
@@ -2283,17 +2520,17 @@
         <v>0</v>
       </c>
       <c r="F28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="4" t="n">
         <v>902</v>
       </c>
-      <c r="G28" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I28" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J28" s="4" t="n">
         <v>0</v>
       </c>
@@ -2325,34 +2562,40 @@
         <v>0</v>
       </c>
       <c r="T28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="U28" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V28" s="4" t="n">
         <v>0</v>
       </c>
       <c r="W28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="X28" s="4" t="n">
-        <v>903</v>
+      <c r="Y28" s="4">
+        <f>SUM(C28:S28)-T28</f>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B29" s="4" t="n">
-        <v>0</v>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>MADADHA.</t>
+        </is>
       </c>
       <c r="C29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D29" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E29" s="4" t="n">
         <v>0</v>
       </c>
@@ -2363,11 +2606,11 @@
         <v>0</v>
       </c>
       <c r="H29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I29" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J29" s="4" t="n">
         <v>0</v>
       </c>
@@ -2378,10 +2621,10 @@
         <v>0</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O29" s="4" t="n">
         <v>0</v>
@@ -2399,34 +2642,40 @@
         <v>0</v>
       </c>
       <c r="T29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="U29" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="X29" s="4" t="n">
         <v>18</v>
+      </c>
+      <c r="Y29" s="4">
+        <f>SUM(C29:S29)-T29</f>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B30" s="4" t="n">
-        <v>0</v>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>MOHMMADAPUR</t>
+        </is>
       </c>
       <c r="C30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="D30" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E30" s="4" t="n">
         <v>0</v>
       </c>
@@ -2452,11 +2701,11 @@
         <v>0</v>
       </c>
       <c r="M30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N30" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O30" s="4" t="n">
         <v>0</v>
       </c>
@@ -2470,37 +2719,43 @@
         <v>0</v>
       </c>
       <c r="S30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="T30" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U30" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W30" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="X30" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="4">
+        <f>SUM(C30:S30)-T30</f>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B31" s="4" t="n">
-        <v>0</v>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>MAHMMADAPOOR</t>
+        </is>
       </c>
       <c r="C31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E31" s="4" t="n">
         <v>0</v>
       </c>
@@ -2511,11 +2766,11 @@
         <v>0</v>
       </c>
       <c r="H31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I31" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J31" s="4" t="n">
         <v>0</v>
       </c>
@@ -2526,10 +2781,10 @@
         <v>0</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O31" s="4" t="n">
         <v>0</v>
@@ -2553,21 +2808,27 @@
         <v>0</v>
       </c>
       <c r="V31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="W31" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="X31" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
+      </c>
+      <c r="Y31" s="4">
+        <f>SUM(C31:S31)-T31</f>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B32" s="4" t="n">
-        <v>0</v>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>NAGARAM</t>
+        </is>
       </c>
       <c r="C32" s="4" t="n">
         <v>0</v>
@@ -2618,11 +2879,11 @@
         <v>0</v>
       </c>
       <c r="S32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="T32" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U32" s="4" t="n">
         <v>0</v>
       </c>
@@ -2630,18 +2891,24 @@
         <v>0</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-1</v>
+        <v>9</v>
+      </c>
+      <c r="Y32" s="4">
+        <f>SUM(C32:S32)-T32</f>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B33" s="4" t="n">
-        <v>0</v>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>POTHARAM(S)</t>
+        </is>
       </c>
       <c r="C33" s="4" t="n">
         <v>0</v>
@@ -2674,11 +2941,11 @@
         <v>0</v>
       </c>
       <c r="M33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="N33" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O33" s="4" t="n">
         <v>0</v>
       </c>
@@ -2707,22 +2974,28 @@
         <v>0</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="4">
+        <f>SUM(C33:S33)-T33</f>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B34" s="4" t="n">
-        <v>0</v>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>POTHARAM(S)</t>
+        </is>
       </c>
       <c r="C34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="D34" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E34" s="4" t="n">
         <v>0</v>
       </c>
@@ -2733,13 +3006,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I34" s="4" t="n">
         <v>9</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>0</v>
@@ -2751,20 +3024,20 @@
         <v>0</v>
       </c>
       <c r="N34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="O34" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P34" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="R34" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" s="4" t="n">
         <v>0</v>
       </c>
@@ -2775,28 +3048,34 @@
         <v>0</v>
       </c>
       <c r="V34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W34" s="4" t="n">
+      <c r="X34" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="X34" s="4" t="n">
-        <v>119</v>
+      <c r="Y34" s="4">
+        <f>SUM(C34:S34)-T34</f>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B35" s="4" t="n">
-        <v>0</v>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>KUCHANPALLT</t>
+        </is>
       </c>
       <c r="C35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="4" t="n">
         <v>902</v>
       </c>
-      <c r="D35" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E35" s="4" t="n">
         <v>0</v>
       </c>
@@ -2822,10 +3101,10 @@
         <v>0</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O35" s="4" t="n">
         <v>0</v>
@@ -2840,46 +3119,52 @@
         <v>0</v>
       </c>
       <c r="S35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="T35" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U35" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W35" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="X35" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="X35" s="4" t="n">
-        <v>905</v>
+      <c r="Y35" s="4">
+        <f>SUM(C35:S35)-T35</f>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B36" s="4" t="n">
-        <v>0</v>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>MATA PAIL</t>
+        </is>
       </c>
       <c r="C36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="4" t="n">
         <v>789</v>
       </c>
-      <c r="D36" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E36" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="4" t="n">
         <v>89</v>
       </c>
-      <c r="G36" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H36" s="4" t="n">
         <v>0</v>
       </c>
@@ -2917,27 +3202,33 @@
         <v>0</v>
       </c>
       <c r="T36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="U36" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="4" t="n">
         <v>182</v>
       </c>
-      <c r="W36" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="X36" s="4" t="n">
-        <v>878</v>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="4">
+        <f>SUM(C36:S36)-T36</f>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B37" s="4" t="n">
-        <v>0</v>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>REGONDA</t>
+        </is>
       </c>
       <c r="C37" s="4" t="n">
         <v>0</v>
@@ -2949,11 +3240,11 @@
         <v>0</v>
       </c>
       <c r="F37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G37" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H37" s="4" t="n">
         <v>0</v>
       </c>
@@ -2973,11 +3264,11 @@
         <v>0</v>
       </c>
       <c r="N37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="O37" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P37" s="4" t="n">
         <v>0</v>
       </c>
@@ -3003,15 +3294,21 @@
         <v>0</v>
       </c>
       <c r="X37" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="4">
+        <f>SUM(C37:S37)-T37</f>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B38" s="4" t="n">
-        <v>0</v>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>GOVARDHANAGIRI</t>
+        </is>
       </c>
       <c r="C38" s="4" t="n">
         <v>0</v>
@@ -3035,10 +3332,10 @@
         <v>0</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L38" s="4" t="n">
         <v>0</v>
@@ -3062,11 +3359,11 @@
         <v>0</v>
       </c>
       <c r="S38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="T38" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U38" s="4" t="n">
         <v>0</v>
       </c>
@@ -3077,22 +3374,28 @@
         <v>0</v>
       </c>
       <c r="X38" s="4" t="n">
-        <v>-60</v>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="4">
+        <f>SUM(C38:S38)-T38</f>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B39" s="4" t="n">
-        <v>0</v>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>GOVARDHANAGIRI</t>
+        </is>
       </c>
       <c r="C39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D39" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
       </c>
@@ -3145,37 +3448,43 @@
         <v>0</v>
       </c>
       <c r="V39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" s="4" t="n">
         <v>6</v>
-      </c>
-      <c r="W39" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="X39" s="4" t="n">
         <v>2</v>
+      </c>
+      <c r="Y39" s="4">
+        <f>SUM(C39:S39)-T39</f>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B40" s="4" t="n">
-        <v>0</v>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>GOVARDHANAGIRI</t>
+        </is>
       </c>
       <c r="C40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="4" t="n">
         <v>98</v>
       </c>
-      <c r="D40" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="G40" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H40" s="4" t="n">
         <v>0</v>
       </c>
@@ -3210,30 +3519,36 @@
         <v>0</v>
       </c>
       <c r="S40" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T40" s="4" t="n">
         <v>8</v>
       </c>
       <c r="U40" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="W40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="X40" s="4" t="n">
-        <v>98</v>
+      <c r="Y40" s="4">
+        <f>SUM(C40:S40)-T40</f>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B41" s="4" t="n">
-        <v>0</v>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>Rao</t>
+        </is>
       </c>
       <c r="C41" s="4" t="n">
         <v>0</v>
@@ -3245,11 +3560,11 @@
         <v>0</v>
       </c>
       <c r="F41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="4" t="n">
         <v>669</v>
       </c>
-      <c r="G41" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H41" s="4" t="n">
         <v>0</v>
       </c>
@@ -3287,43 +3602,49 @@
         <v>0</v>
       </c>
       <c r="T41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="U41" s="4" t="n">
+      <c r="V41" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="V41" s="4" t="n">
+      <c r="W41" s="4" t="n">
         <v>692</v>
       </c>
-      <c r="W41" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="X41" s="4" t="n">
-        <v>669</v>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="4">
+        <f>SUM(C41:S41)-T41</f>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B42" s="4" t="n">
-        <v>0</v>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>Lancer</t>
+        </is>
       </c>
       <c r="C42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="D42" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E42" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="G42" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H42" s="4" t="n">
         <v>0</v>
       </c>
@@ -3340,11 +3661,11 @@
         <v>0</v>
       </c>
       <c r="M42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="N42" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O42" s="4" t="n">
         <v>0</v>
       </c>
@@ -3367,21 +3688,27 @@
         <v>0</v>
       </c>
       <c r="V42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" s="4" t="n">
         <v>98</v>
       </c>
-      <c r="W42" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="X42" s="4" t="n">
-        <v>148</v>
+        <v>9</v>
+      </c>
+      <c r="Y42" s="4">
+        <f>SUM(C42:S42)-T42</f>
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B43" s="4" t="n">
-        <v>0</v>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>NANNARAM</t>
+        </is>
       </c>
       <c r="C43" s="4" t="n">
         <v>0</v>
@@ -3417,10 +3744,10 @@
         <v>0</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P43" s="4" t="n">
         <v>0</v>
@@ -3432,30 +3759,36 @@
         <v>0</v>
       </c>
       <c r="S43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="T43" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U43" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V43" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W43" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X43" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="4">
+        <f>SUM(C43:S43)-T43</f>
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B44" s="4" t="n">
-        <v>0</v>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>POTHARAM(N</t>
+        </is>
       </c>
       <c r="C44" s="4" t="n">
         <v>0</v>
@@ -3482,11 +3815,11 @@
         <v>0</v>
       </c>
       <c r="K44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L44" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M44" s="4" t="n">
         <v>0</v>
       </c>
@@ -3506,37 +3839,43 @@
         <v>0</v>
       </c>
       <c r="S44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="T44" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U44" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="W44" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="X44" s="4" t="n">
-        <v>-58</v>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="4">
+        <f>SUM(C44:S44)-T44</f>
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B45" s="4" t="n">
-        <v>0</v>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>RAMAVARAM.</t>
+        </is>
       </c>
       <c r="C45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="4" t="n">
         <v>82</v>
       </c>
-      <c r="D45" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E45" s="4" t="n">
         <v>0</v>
       </c>
@@ -3580,37 +3919,43 @@
         <v>0</v>
       </c>
       <c r="S45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" s="4" t="n">
         <v>602</v>
       </c>
-      <c r="T45" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U45" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" s="4" t="n">
         <v>691</v>
       </c>
-      <c r="W45" s="4" t="n">
+      <c r="X45" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="X45" s="4" t="n">
-        <v>-520</v>
+      <c r="Y45" s="4">
+        <f>SUM(C45:S45)-T45</f>
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B46" s="4" t="n">
-        <v>0</v>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>RAMAVARAM</t>
+        </is>
       </c>
       <c r="C46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="4" t="n">
         <v>972</v>
       </c>
-      <c r="D46" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E46" s="4" t="n">
         <v>0</v>
       </c>
@@ -3618,82 +3963,88 @@
         <v>0</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L46" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="M46" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M46" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="N46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="O46" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P46" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R46" s="4" t="n">
         <v>4</v>
       </c>
       <c r="S46" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T46" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="T46" s="4" t="n">
+      <c r="U46" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="U46" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V46" s="4" t="n">
         <v>0</v>
       </c>
       <c r="W46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="X46" s="4" t="n">
-        <v>1016</v>
+      <c r="Y46" s="4">
+        <f>SUM(C46:S46)-T46</f>
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="B47" s="4" t="n">
-        <v>0</v>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>GANDIPATIT</t>
+        </is>
       </c>
       <c r="C47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="4" t="n">
         <v>798</v>
       </c>
-      <c r="D47" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E47" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="G47" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H47" s="4" t="n">
         <v>0</v>
       </c>
@@ -3728,11 +4079,11 @@
         <v>0</v>
       </c>
       <c r="S47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" s="4" t="n">
         <v>922</v>
       </c>
-      <c r="T47" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U47" s="4" t="n">
         <v>0</v>
       </c>
@@ -3743,15 +4094,21 @@
         <v>0</v>
       </c>
       <c r="X47" s="4" t="n">
-        <v>-118</v>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="4">
+        <f>SUM(C47:S47)-T47</f>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B48" s="4" t="n">
-        <v>0</v>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>KUNDANVANI PALLI</t>
+        </is>
       </c>
       <c r="C48" s="4" t="n">
         <v>0</v>
@@ -3787,51 +4144,57 @@
         <v>0</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Q48" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="4" t="n">
         <v>827</v>
       </c>
-      <c r="T48" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="U48" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="W48" s="4" t="n">
+      <c r="X48" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="X48" s="4" t="n">
-        <v>-814</v>
+      <c r="Y48" s="4">
+        <f>SUM(C48:S48)-T48</f>
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B49" s="4" t="n">
-        <v>0</v>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>Me Avata vac</t>
+        </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E49" s="4" t="n">
         <v>0</v>
@@ -3858,10 +4221,10 @@
         <v>0</v>
       </c>
       <c r="M49" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O49" s="4" t="n">
         <v>0</v>
@@ -3876,10 +4239,10 @@
         <v>0</v>
       </c>
       <c r="S49" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="T49" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U49" s="4" t="n">
         <v>0</v>
@@ -3891,43 +4254,49 @@
         <v>0</v>
       </c>
       <c r="X49" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="4">
+        <f>SUM(C49:S49)-T49</f>
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B50" s="4" t="n">
-        <v>0</v>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>IGANDIPALLI</t>
+        </is>
       </c>
       <c r="C50" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E50" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F50" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H50" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="I50" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K50" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="L50" s="4" t="n">
         <v>0</v>
       </c>
@@ -3935,49 +4304,55 @@
         <v>0</v>
       </c>
       <c r="N50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="O50" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P50" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R50" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="4" t="n">
         <v>79</v>
       </c>
-      <c r="T50" s="4" t="n">
+      <c r="U50" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="U50" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V50" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W50" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X50" s="4" t="n">
-        <v>-37</v>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="4">
+        <f>SUM(C50:S50)-T50</f>
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B51" s="4" t="n">
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>IGOURA VELL!</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C51" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D51" s="4" t="n">
         <v>0</v>
       </c>
@@ -3985,17 +4360,17 @@
         <v>0</v>
       </c>
       <c r="F51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="H51" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="H51" s="4" t="n">
+      <c r="I51" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I51" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J51" s="4" t="n">
         <v>0</v>
       </c>
@@ -4015,19 +4390,19 @@
         <v>0</v>
       </c>
       <c r="P51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="Q51" s="4" t="n">
+      <c r="R51" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="R51" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S51" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="T51" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U51" s="4" t="n">
         <v>0</v>
@@ -4036,18 +4411,24 @@
         <v>0</v>
       </c>
       <c r="W51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="X51" s="4" t="n">
-        <v>25</v>
+      <c r="Y51" s="4">
+        <f>SUM(C51:S51)-T51</f>
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B52" s="4" t="n">
-        <v>0</v>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>IGOURA VELLI</t>
+        </is>
       </c>
       <c r="C52" s="4" t="n">
         <v>0</v>
@@ -4059,20 +4440,20 @@
         <v>0</v>
       </c>
       <c r="F52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="G52" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H52" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J52" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K52" s="4" t="n">
         <v>0</v>
       </c>
@@ -4098,13 +4479,13 @@
         <v>0</v>
       </c>
       <c r="S52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="4" t="n">
         <v>89</v>
       </c>
-      <c r="T52" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="U52" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V52" s="4" t="n">
         <v>0</v>
@@ -4113,15 +4494,21 @@
         <v>0</v>
       </c>
       <c r="X52" s="4" t="n">
-        <v>-81</v>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="4">
+        <f>SUM(C52:S52)-T52</f>
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B53" s="4" t="n">
-        <v>0</v>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>IGUDATI PALLI</t>
+        </is>
       </c>
       <c r="C53" s="4" t="n">
         <v>0</v>
@@ -4130,11 +4517,11 @@
         <v>0</v>
       </c>
       <c r="E53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F53" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="G53" s="4" t="n">
         <v>0</v>
       </c>
@@ -4142,11 +4529,11 @@
         <v>0</v>
       </c>
       <c r="I53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="J53" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K53" s="4" t="n">
         <v>0</v>
       </c>
@@ -4157,11 +4544,11 @@
         <v>0</v>
       </c>
       <c r="N53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="O53" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P53" s="4" t="n">
         <v>0</v>
       </c>
@@ -4172,34 +4559,40 @@
         <v>0</v>
       </c>
       <c r="S53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="T53" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U53" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V53" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W53" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X53" s="4" t="n">
-        <v>63</v>
+        <v>0</v>
+      </c>
+      <c r="Y53" s="4">
+        <f>SUM(C53:S53)-T53</f>
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="B54" s="4" t="n">
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>ITENUGU PALLI</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="C54" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D54" s="4" t="n">
         <v>0</v>
       </c>
@@ -4207,17 +4600,17 @@
         <v>0</v>
       </c>
       <c r="F54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="G54" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="I54" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J54" s="4" t="n">
         <v>0</v>
       </c>
@@ -4228,11 +4621,11 @@
         <v>0</v>
       </c>
       <c r="M54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N54" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O54" s="4" t="n">
         <v>0</v>
       </c>
@@ -4246,30 +4639,36 @@
         <v>0</v>
       </c>
       <c r="S54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="T54" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U54" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="W54" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="X54" s="4" t="n">
-        <v>77</v>
+        <v>0</v>
+      </c>
+      <c r="Y54" s="4">
+        <f>SUM(C54:S54)-T54</f>
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="B55" s="4" t="n">
-        <v>0</v>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>JANAGAM</t>
+        </is>
       </c>
       <c r="C55" s="4" t="n">
         <v>0</v>
@@ -4284,17 +4683,17 @@
         <v>0</v>
       </c>
       <c r="G55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H55" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="J55" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K55" s="4" t="n">
         <v>0</v>
       </c>
@@ -4320,11 +4719,11 @@
         <v>0</v>
       </c>
       <c r="S55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="T55" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U55" s="4" t="n">
         <v>0</v>
       </c>
@@ -4335,15 +4734,21 @@
         <v>0</v>
       </c>
       <c r="X55" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
+      </c>
+      <c r="Y55" s="4">
+        <f>SUM(C55:S55)-T55</f>
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="B56" s="4" t="n">
-        <v>0</v>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>JANAGAM</t>
+        </is>
       </c>
       <c r="C56" s="4" t="n">
         <v>0</v>
@@ -4364,11 +4769,11 @@
         <v>0</v>
       </c>
       <c r="I56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="J56" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K56" s="4" t="n">
         <v>0</v>
       </c>
@@ -4376,11 +4781,11 @@
         <v>0</v>
       </c>
       <c r="M56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="N56" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O56" s="4" t="n">
         <v>0</v>
       </c>
@@ -4394,40 +4799,46 @@
         <v>0</v>
       </c>
       <c r="S56" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="T56" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U56" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V56" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="W56" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="W56" s="4" t="n">
+      <c r="X56" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="X56" s="4" t="n">
-        <v>-1</v>
+      <c r="Y56" s="4">
+        <f>SUM(C56:S56)-T56</f>
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="B57" s="4" t="n">
-        <v>0</v>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>JJANAGAM</t>
+        </is>
       </c>
       <c r="C57" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E57" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F57" s="4" t="n">
         <v>0</v>
       </c>
@@ -4480,18 +4891,24 @@
         <v>0</v>
       </c>
       <c r="W57" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="X57" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="Y57" s="4">
+        <f>SUM(C57:S57)-T57</f>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="B58" s="4" t="n">
-        <v>0</v>
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>GUBBADI J</t>
+        </is>
       </c>
       <c r="C58" s="4" t="n">
         <v>0</v>
@@ -4503,11 +4920,11 @@
         <v>0</v>
       </c>
       <c r="F58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="G58" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H58" s="4" t="n">
         <v>0</v>
       </c>
@@ -4524,48 +4941,54 @@
         <v>0</v>
       </c>
       <c r="M58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="N58" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="P58" s="4" t="n">
+      <c r="Q58" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q58" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="T58" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U58" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="W58" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="X58" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="Y58" s="4">
+        <f>SUM(C58:S58)-T58</f>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="B59" s="4" t="n">
-        <v>0</v>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>—z 1</t>
+        </is>
       </c>
       <c r="C59" s="4" t="n">
         <v>0</v>
@@ -4577,11 +5000,11 @@
         <v>0</v>
       </c>
       <c r="F59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="G59" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H59" s="4" t="n">
         <v>0</v>
       </c>
@@ -4601,11 +5024,11 @@
         <v>0</v>
       </c>
       <c r="N59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="O59" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P59" s="4" t="n">
         <v>0</v>
       </c>
@@ -4631,15 +5054,21 @@
         <v>0</v>
       </c>
       <c r="X59" s="4" t="n">
-        <v>64</v>
+        <v>0</v>
+      </c>
+      <c r="Y59" s="4">
+        <f>SUM(C59:S59)-T59</f>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="B60" s="4" t="n">
-        <v>0</v>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>THOTA PALI SY</t>
+        </is>
       </c>
       <c r="C60" s="4" t="n">
         <v>0</v>
@@ -4651,11 +5080,11 @@
         <v>0</v>
       </c>
       <c r="F60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G60" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H60" s="4" t="n">
         <v>0</v>
       </c>
@@ -4678,11 +5107,11 @@
         <v>0</v>
       </c>
       <c r="O60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="P60" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q60" s="4" t="n">
         <v>0</v>
       </c>
@@ -4690,37 +5119,43 @@
         <v>0</v>
       </c>
       <c r="S60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="4" t="n">
         <v>287</v>
       </c>
-      <c r="T60" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="V60" s="4" t="n">
+      <c r="W60" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="W60" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="X60" s="4" t="n">
-        <v>-281</v>
+        <v>0</v>
+      </c>
+      <c r="Y60" s="4">
+        <f>SUM(C60:S60)-T60</f>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="B61" s="4" t="n">
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>RANDHINAGAR</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C61" s="4" t="n">
+      <c r="D61" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="D61" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E61" s="4" t="n">
         <v>0</v>
       </c>
@@ -4746,64 +5181,70 @@
         <v>0</v>
       </c>
       <c r="M61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="4" t="n">
         <v>82</v>
       </c>
-      <c r="N61" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="O61" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="Q61" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="4" t="n">
         <v>897</v>
       </c>
-      <c r="T61" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="U61" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="W61" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="X61" s="4" t="n">
-        <v>-789</v>
+        <v>0</v>
+      </c>
+      <c r="Y61" s="4">
+        <f>SUM(C61:S61)-T61</f>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="B62" s="4" t="n">
-        <v>0</v>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>ANTAKKA PFTA</t>
+        </is>
       </c>
       <c r="C62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="4" t="n">
         <v>269</v>
       </c>
-      <c r="D62" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E62" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="4" t="n">
         <v>689</v>
       </c>
-      <c r="G62" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H62" s="4" t="n">
         <v>0</v>
       </c>
@@ -4820,11 +5261,11 @@
         <v>0</v>
       </c>
       <c r="M62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N62" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O62" s="4" t="n">
         <v>0</v>
       </c>
@@ -4838,37 +5279,43 @@
         <v>0</v>
       </c>
       <c r="S62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="T62" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="V62" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="W62" s="4" t="n">
         <v>0</v>
       </c>
       <c r="X62" s="4" t="n">
-        <v>960</v>
+        <v>0</v>
+      </c>
+      <c r="Y62" s="4">
+        <f>SUM(C62:S62)-T62</f>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="B63" s="4" t="n">
-        <v>0</v>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>ANTHAKKAPFT.</t>
+        </is>
       </c>
       <c r="C63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="D63" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E63" s="4" t="n">
         <v>0</v>
       </c>
@@ -4879,11 +5326,11 @@
         <v>0</v>
       </c>
       <c r="H63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="I63" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J63" s="4" t="n">
         <v>0</v>
       </c>
@@ -4891,23 +5338,23 @@
         <v>0</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M63" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="N63" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="N63" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="P63" s="4" t="n">
+      <c r="Q63" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="Q63" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" s="4" t="n">
         <v>0</v>
       </c>
@@ -4918,31 +5365,37 @@
         <v>0</v>
       </c>
       <c r="U63" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V63" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="W63" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="W63" s="4" t="n">
+      <c r="X63" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="X63" s="4" t="n">
-        <v>117</v>
+      <c r="Y63" s="4">
+        <f>SUM(C63:S63)-T63</f>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="B64" s="4" t="n">
-        <v>0</v>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>ANTAKKA PFTA</t>
+        </is>
       </c>
       <c r="C64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D64" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E64" s="4" t="n">
         <v>0</v>
       </c>
@@ -4968,11 +5421,11 @@
         <v>0</v>
       </c>
       <c r="M64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="N64" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O64" s="4" t="n">
         <v>0</v>
       </c>
@@ -4986,10 +5439,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="T64" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U64" s="4" t="n">
         <v>0</v>
@@ -4998,34 +5451,40 @@
         <v>0</v>
       </c>
       <c r="W64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="X64" s="4" t="n">
-        <v>-5</v>
+      <c r="Y64" s="4">
+        <f>SUM(C64:S64)-T64</f>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="B65" s="4" t="n">
-        <v>0</v>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>ANTHAKKAPFT</t>
+        </is>
       </c>
       <c r="C65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D65" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="E65" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="G65" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H65" s="4" t="n">
         <v>0</v>
       </c>
@@ -5033,20 +5492,20 @@
         <v>0</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>8</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="N65" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O65" s="4" t="n">
         <v>0</v>
       </c>
@@ -5057,14 +5516,14 @@
         <v>0</v>
       </c>
       <c r="R65" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S65" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="T65" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="T65" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U65" s="4" t="n">
         <v>0</v>
       </c>
@@ -5072,34 +5531,40 @@
         <v>0</v>
       </c>
       <c r="W65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" s="4" t="n">
         <v>82</v>
       </c>
-      <c r="X65" s="4" t="n">
-        <v>138</v>
+      <c r="Y65" s="4">
+        <f>SUM(C65:S65)-T65</f>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="B66" s="4" t="n">
-        <v>0</v>
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>WANNA PETA</t>
+        </is>
       </c>
       <c r="C66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D66" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E66" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="G66" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H66" s="4" t="n">
         <v>0</v>
       </c>
@@ -5116,10 +5581,10 @@
         <v>0</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O66" s="4" t="n">
         <v>0</v>
@@ -5134,30 +5599,36 @@
         <v>0</v>
       </c>
       <c r="S66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="T66" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V66" s="4" t="n">
+      <c r="W66" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W66" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="X66" s="4" t="n">
-        <v>67</v>
+        <v>0</v>
+      </c>
+      <c r="Y66" s="4">
+        <f>SUM(C66:S66)-T66</f>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="B67" s="4" t="n">
-        <v>0</v>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>AKANNA PFTA</t>
+        </is>
       </c>
       <c r="C67" s="4" t="n">
         <v>0</v>
@@ -5172,17 +5643,17 @@
         <v>0</v>
       </c>
       <c r="G67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H67" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J67" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K67" s="4" t="n">
         <v>0</v>
       </c>
@@ -5208,46 +5679,52 @@
         <v>0</v>
       </c>
       <c r="S67" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="T67" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U67" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" s="4" t="n">
         <v>82</v>
       </c>
-      <c r="W67" s="4" t="n">
+      <c r="X67" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="X67" s="4" t="n">
-        <v>-2</v>
+      <c r="Y67" s="4">
+        <f>SUM(C67:S67)-T67</f>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="B68" s="4" t="n">
-        <v>0</v>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>DaNTHIN THANNA</t>
+        </is>
       </c>
       <c r="C68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D68" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E68" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="G68" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H68" s="4" t="n">
         <v>0</v>
       </c>
@@ -5258,17 +5735,17 @@
         <v>0</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="4" t="n">
         <v>82</v>
       </c>
-      <c r="N68" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O68" s="4" t="n">
         <v>0</v>
       </c>
@@ -5282,30 +5759,36 @@
         <v>0</v>
       </c>
       <c r="S68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" s="4" t="n">
         <v>92</v>
       </c>
-      <c r="T68" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="V68" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="W68" s="4" t="n">
         <v>0</v>
       </c>
       <c r="X68" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
+      </c>
+      <c r="Y68" s="4">
+        <f>SUM(C68:S68)-T68</f>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="B69" s="4" t="n">
-        <v>0</v>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>KESHANAYAK THANDA</t>
+        </is>
       </c>
       <c r="C69" s="4" t="n">
         <v>0</v>
@@ -5317,14 +5800,14 @@
         <v>0</v>
       </c>
       <c r="F69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="G69" s="4" t="n">
+      <c r="H69" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H69" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I69" s="4" t="n">
         <v>0</v>
       </c>
@@ -5341,11 +5824,11 @@
         <v>0</v>
       </c>
       <c r="N69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="O69" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P69" s="4" t="n">
         <v>0</v>
       </c>
@@ -5356,11 +5839,11 @@
         <v>0</v>
       </c>
       <c r="S69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" s="4" t="n">
         <v>902</v>
       </c>
-      <c r="T69" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U69" s="4" t="n">
         <v>0</v>
       </c>
@@ -5371,15 +5854,21 @@
         <v>0</v>
       </c>
       <c r="X69" s="4" t="n">
-        <v>-835</v>
+        <v>0</v>
+      </c>
+      <c r="Y69" s="4">
+        <f>SUM(C69:S69)-T69</f>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="B70" s="4" t="n">
-        <v>0</v>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>KKANNAPFT</t>
+        </is>
       </c>
       <c r="C70" s="4" t="n">
         <v>0</v>
@@ -5391,19 +5880,19 @@
         <v>0</v>
       </c>
       <c r="F70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="G70" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H70" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>0</v>
@@ -5415,11 +5904,11 @@
         <v>0</v>
       </c>
       <c r="N70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="O70" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P70" s="4" t="n">
         <v>0</v>
       </c>
@@ -5442,40 +5931,46 @@
         <v>0</v>
       </c>
       <c r="W70" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="X70" s="4" t="n">
-        <v>77</v>
+        <v>9</v>
+      </c>
+      <c r="Y70" s="4">
+        <f>SUM(C70:S70)-T70</f>
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="B71" s="4" t="n">
-        <v>0</v>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>TT FT AGANNA</t>
+        </is>
       </c>
       <c r="C71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="D71" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E71" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G71" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I71" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J71" s="4" t="n">
         <v>0</v>
       </c>
@@ -5489,26 +5984,26 @@
         <v>0</v>
       </c>
       <c r="N71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="O71" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P71" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q71" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R71" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="T71" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U71" s="4" t="n">
         <v>0</v>
       </c>
@@ -5519,31 +6014,37 @@
         <v>0</v>
       </c>
       <c r="X71" s="4" t="n">
-        <v>-27</v>
+        <v>0</v>
+      </c>
+      <c r="Y71" s="4">
+        <f>SUM(C71:S71)-T71</f>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="B72" s="4" t="n">
-        <v>0</v>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>TIMMAPLIR</t>
+        </is>
       </c>
       <c r="C72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="D72" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E72" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="4" t="n">
         <v>99</v>
       </c>
-      <c r="G72" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H72" s="4" t="n">
         <v>0</v>
       </c>
@@ -5563,11 +6064,11 @@
         <v>0</v>
       </c>
       <c r="N72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="O72" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P72" s="4" t="n">
         <v>0</v>
       </c>
@@ -5578,30 +6079,36 @@
         <v>0</v>
       </c>
       <c r="S72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T72" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="U72" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="V72" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V72" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="W72" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X72" s="4" t="n">
-        <v>133</v>
+        <v>0</v>
+      </c>
+      <c r="Y72" s="4">
+        <f>SUM(C72:S72)-T72</f>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="B73" s="4" t="n">
-        <v>0</v>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>MIRZAPLIR</t>
+        </is>
       </c>
       <c r="C73" s="4" t="n">
         <v>0</v>
@@ -5661,43 +6168,49 @@
         <v>0</v>
       </c>
       <c r="V73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W73" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="X73" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y73" s="4">
+        <f>SUM(C73:S73)-T73</f>
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="B74" s="4" t="n">
-        <v>0</v>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>MiR7APLIR</t>
+        </is>
       </c>
       <c r="C74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D74" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E74" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="G74" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I74" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J74" s="4" t="n">
         <v>0</v>
       </c>
@@ -5705,13 +6218,13 @@
         <v>0</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" s="4" t="n">
         <v>1</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O74" s="4" t="n">
         <v>0</v>
@@ -5735,21 +6248,28 @@
         <v>0</v>
       </c>
       <c r="V74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" s="4" t="n">
         <v>661</v>
       </c>
-      <c r="W74" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="X74" s="4" t="n">
-        <v>22</v>
+        <v>0</v>
+      </c>
+      <c r="Y74" s="4">
+        <f>SUM(C74:S74)-T74</f>
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="B75" s="4" t="n">
-        <v>0</v>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>Mandal Parishad Upper Primary
+School Keshavapur (South) Wing</t>
+        </is>
       </c>
       <c r="C75" s="4" t="n">
         <v>0</v>
@@ -5803,43 +6323,49 @@
         <v>0</v>
       </c>
       <c r="T75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="U75" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="W75" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="X75" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="Y75" s="4">
+        <f>SUM(C75:S75)-T75</f>
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="B76" s="4" t="n">
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>Yecuavapie</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="C76" s="4" t="n">
+      <c r="D76" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="D76" s="4" t="n">
+      <c r="E76" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E76" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="4" t="n">
         <v>99</v>
       </c>
-      <c r="G76" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H76" s="4" t="n">
         <v>0</v>
       </c>
@@ -5859,10 +6385,10 @@
         <v>0</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P76" s="4" t="n">
         <v>0</v>
@@ -5889,34 +6415,40 @@
         <v>0</v>
       </c>
       <c r="X76" s="4" t="n">
-        <v>151</v>
+        <v>0</v>
+      </c>
+      <c r="Y76" s="4">
+        <f>SUM(C76:S76)-T76</f>
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="B77" s="4" t="n">
-        <v>0</v>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>WESHAVAPIIR</t>
+        </is>
       </c>
       <c r="C77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="D77" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E77" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G77" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H77" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H77" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I77" s="4" t="n">
         <v>0</v>
       </c>
@@ -5948,11 +6480,11 @@
         <v>0</v>
       </c>
       <c r="S77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" s="4" t="n">
         <v>901</v>
       </c>
-      <c r="T77" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U77" s="4" t="n">
         <v>0</v>
       </c>
@@ -5963,15 +6495,21 @@
         <v>0</v>
       </c>
       <c r="X77" s="4" t="n">
-        <v>-869</v>
+        <v>0</v>
+      </c>
+      <c r="Y77" s="4">
+        <f>SUM(C77:S77)-T77</f>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="B78" s="4" t="n">
-        <v>0</v>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>PuanTAPArIt</t>
+        </is>
       </c>
       <c r="C78" s="4" t="n">
         <v>0</v>
@@ -5989,28 +6527,28 @@
         <v>0</v>
       </c>
       <c r="H78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I78" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J78" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L78" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="N78" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="O78" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P78" s="4" t="n">
         <v>0</v>
@@ -6022,30 +6560,36 @@
         <v>0</v>
       </c>
       <c r="S78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T78" s="4" t="n">
+      <c r="U78" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="U78" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" s="4" t="n">
         <v>89</v>
       </c>
-      <c r="W78" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="X78" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
+      </c>
+      <c r="Y78" s="4">
+        <f>SUM(C78:S78)-T78</f>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="B79" s="4" t="n">
-        <v>0</v>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>HONTAPATIT</t>
+        </is>
       </c>
       <c r="C79" s="4" t="n">
         <v>0</v>
@@ -6054,11 +6598,11 @@
         <v>0</v>
       </c>
       <c r="E79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F79" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="G79" s="4" t="n">
         <v>0</v>
       </c>
@@ -6087,19 +6631,19 @@
         <v>0</v>
       </c>
       <c r="P79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="Q79" s="4" t="n">
+      <c r="R79" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="R79" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S79" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="T79" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U79" s="4" t="n">
         <v>0</v>
@@ -6108,39 +6652,45 @@
         <v>0</v>
       </c>
       <c r="W79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="X79" s="4" t="n">
-        <v>7</v>
+      <c r="Y79" s="4">
+        <f>SUM(C79:S79)-T79</f>
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="B80" s="4" t="n">
-        <v>0</v>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>Mai 1 AMAPAII1</t>
+        </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E80" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>0</v>
@@ -6155,11 +6705,11 @@
         <v>0</v>
       </c>
       <c r="N80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="O80" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P80" s="4" t="n">
         <v>0</v>
       </c>
@@ -6167,14 +6717,14 @@
         <v>0</v>
       </c>
       <c r="R80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="S80" s="4" t="n">
+      <c r="T80" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="T80" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U80" s="4" t="n">
         <v>0</v>
       </c>
@@ -6182,25 +6732,31 @@
         <v>0</v>
       </c>
       <c r="W80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="X80" s="4" t="n">
-        <v>31</v>
+      <c r="Y80" s="4">
+        <f>SUM(C80:S80)-T80</f>
+        <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="B81" s="4" t="n">
-        <v>0</v>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>naar ANAPAL IT</t>
+        </is>
       </c>
       <c r="C81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D81" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E81" s="4" t="n">
         <v>0</v>
       </c>
@@ -6214,23 +6770,23 @@
         <v>0</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L81" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N81" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O81" s="4" t="n">
         <v>0</v>
       </c>
@@ -6241,14 +6797,14 @@
         <v>0</v>
       </c>
       <c r="R81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="S81" s="4" t="n">
+      <c r="T81" s="4" t="n">
         <v>292</v>
       </c>
-      <c r="T81" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U81" s="4" t="n">
         <v>0</v>
       </c>
@@ -6256,18 +6812,24 @@
         <v>0</v>
       </c>
       <c r="W81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X81" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="X81" s="4" t="n">
-        <v>-216</v>
+      <c r="Y81" s="4">
+        <f>SUM(C81:S81)-T81</f>
+        <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="B82" s="4" t="n">
-        <v>0</v>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>Rea mala</t>
+        </is>
       </c>
       <c r="C82" s="4" t="n">
         <v>0</v>
@@ -6300,11 +6862,11 @@
         <v>0</v>
       </c>
       <c r="M82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="N82" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O82" s="4" t="n">
         <v>0</v>
       </c>
@@ -6318,46 +6880,52 @@
         <v>0</v>
       </c>
       <c r="S82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T82" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U82" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V82" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W82" s="4" t="n">
         <v>2</v>
       </c>
       <c r="X82" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="Y82" s="4">
+        <f>SUM(C82:S82)-T82</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="B83" s="4" t="n">
-        <v>0</v>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>IWaRIKOI It</t>
+        </is>
       </c>
       <c r="C83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="4" t="n">
         <v>208</v>
       </c>
-      <c r="D83" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E83" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="G83" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H83" s="4" t="n">
         <v>0</v>
       </c>
@@ -6377,10 +6945,10 @@
         <v>0</v>
       </c>
       <c r="N83" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O83" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P83" s="4" t="n">
         <v>0</v>
@@ -6401,37 +6969,43 @@
         <v>0</v>
       </c>
       <c r="V83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" s="4" t="n">
         <v>882</v>
       </c>
-      <c r="W83" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="X83" s="4" t="n">
-        <v>259</v>
+        <v>0</v>
+      </c>
+      <c r="Y83" s="4">
+        <f>SUM(C83:S83)-T83</f>
+        <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
         <v>79</v>
       </c>
-      <c r="B84" s="4" t="n">
-        <v>0</v>
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>Napialit</t>
+        </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E84" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="4" t="n">
         <v>89</v>
       </c>
-      <c r="G84" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H84" s="4" t="n">
         <v>0</v>
       </c>
@@ -6442,20 +7016,20 @@
         <v>0</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="N84" s="4" t="n">
+      <c r="O84" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="O84" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P84" s="4" t="n">
         <v>0</v>
       </c>
@@ -6475,21 +7049,27 @@
         <v>0</v>
       </c>
       <c r="V84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W84" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="W84" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="X84" s="4" t="n">
-        <v>119</v>
+        <v>0</v>
+      </c>
+      <c r="Y84" s="4">
+        <f>SUM(C84:S84)-T84</f>
+        <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="B85" s="4" t="n">
-        <v>0</v>
+      <c r="B85" s="14" t="inlineStr">
+        <is>
+          <t>PAMCHANNRAPIIR</t>
+        </is>
       </c>
       <c r="C85" s="4" t="n">
         <v>0</v>
@@ -6501,16 +7081,16 @@
         <v>0</v>
       </c>
       <c r="F85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G85" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H85" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>0</v>
@@ -6546,40 +7126,46 @@
         <v>0</v>
       </c>
       <c r="U85" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V85" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="W85" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="W85" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="X85" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
+      </c>
+      <c r="Y85" s="4">
+        <f>SUM(C85:S85)-T85</f>
+        <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
         <v>81</v>
       </c>
-      <c r="B86" s="4" t="n">
-        <v>0</v>
+      <c r="B86" s="14" t="inlineStr">
+        <is>
+          <t>SARAALANINDAPIIR</t>
+        </is>
       </c>
       <c r="C86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D86" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E86" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="G86" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H86" s="4" t="n">
         <v>0</v>
       </c>
@@ -6596,11 +7182,11 @@
         <v>0</v>
       </c>
       <c r="M86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="N86" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O86" s="4" t="n">
         <v>0</v>
       </c>
@@ -6614,13 +7200,13 @@
         <v>0</v>
       </c>
       <c r="S86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" s="4" t="n">
         <v>182</v>
       </c>
-      <c r="T86" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="U86" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V86" s="4" t="n">
         <v>0</v>
@@ -6629,101 +7215,284 @@
         <v>0</v>
       </c>
       <c r="X86" s="4" t="n">
-        <v>-169</v>
+        <v>0</v>
+      </c>
+      <c r="Y86" s="4">
+        <f>SUM(C86:S86)-T86</f>
+        <v/>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B87" s="6">
-        <f>SUM(B6:B86)</f>
-        <v/>
-      </c>
-      <c r="C87" s="6">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL EVM VOTES</t>
+        </is>
+      </c>
+      <c r="C87" s="8">
         <f>SUM(C6:C86)</f>
         <v/>
       </c>
-      <c r="D87" s="6">
+      <c r="D87" s="8">
         <f>SUM(D6:D86)</f>
         <v/>
       </c>
-      <c r="E87" s="6">
+      <c r="E87" s="8">
         <f>SUM(E6:E86)</f>
         <v/>
       </c>
-      <c r="F87" s="6">
+      <c r="F87" s="8">
         <f>SUM(F6:F86)</f>
         <v/>
       </c>
-      <c r="G87" s="6">
+      <c r="G87" s="8">
         <f>SUM(G6:G86)</f>
         <v/>
       </c>
-      <c r="H87" s="6">
+      <c r="H87" s="8">
         <f>SUM(H6:H86)</f>
         <v/>
       </c>
-      <c r="I87" s="6">
+      <c r="I87" s="8">
         <f>SUM(I6:I86)</f>
         <v/>
       </c>
-      <c r="J87" s="6">
+      <c r="J87" s="8">
         <f>SUM(J6:J86)</f>
         <v/>
       </c>
-      <c r="K87" s="6">
+      <c r="K87" s="8">
         <f>SUM(K6:K86)</f>
         <v/>
       </c>
-      <c r="L87" s="6">
+      <c r="L87" s="8">
         <f>SUM(L6:L86)</f>
         <v/>
       </c>
-      <c r="M87" s="6">
+      <c r="M87" s="8">
         <f>SUM(M6:M86)</f>
         <v/>
       </c>
-      <c r="N87" s="6">
+      <c r="N87" s="8">
         <f>SUM(N6:N86)</f>
         <v/>
       </c>
-      <c r="O87" s="6">
+      <c r="O87" s="8">
         <f>SUM(O6:O86)</f>
         <v/>
       </c>
-      <c r="P87" s="6">
+      <c r="P87" s="8">
         <f>SUM(P6:P86)</f>
         <v/>
       </c>
-      <c r="Q87" s="6">
+      <c r="Q87" s="8">
         <f>SUM(Q6:Q86)</f>
         <v/>
       </c>
-      <c r="R87" s="6">
+      <c r="R87" s="8">
         <f>SUM(R6:R86)</f>
         <v/>
       </c>
-      <c r="S87" s="6">
+      <c r="S87" s="8">
         <f>SUM(S6:S86)</f>
         <v/>
       </c>
-      <c r="T87" s="6">
+      <c r="T87" s="8">
         <f>SUM(T6:T86)</f>
         <v/>
       </c>
-      <c r="U87" s="6">
+      <c r="U87" s="8">
         <f>SUM(U6:U86)</f>
         <v/>
       </c>
-      <c r="V87" s="6">
+      <c r="V87" s="8">
         <f>SUM(V6:V86)</f>
         <v/>
       </c>
-      <c r="W87" s="6">
-        <f>SUM(W6:W86)</f>
+      <c r="W87" s="8">
+        <f>T87+U87</f>
+        <v/>
+      </c>
+      <c r="X87" s="8">
+        <f>SUM(X6:X86)</f>
+        <v/>
+      </c>
+      <c r="Y87" s="8">
+        <f>SUM(C87:S87)-T87</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>POSTAL BALLOT VOTES</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL VOTES POLLED</t>
+        </is>
+      </c>
+      <c r="C89" s="12">
+        <f>C87+C88</f>
+        <v/>
+      </c>
+      <c r="D89" s="12">
+        <f>D87+D88</f>
+        <v/>
+      </c>
+      <c r="E89" s="12">
+        <f>E87+E88</f>
+        <v/>
+      </c>
+      <c r="F89" s="12">
+        <f>F87+F88</f>
+        <v/>
+      </c>
+      <c r="G89" s="12">
+        <f>G87+G88</f>
+        <v/>
+      </c>
+      <c r="H89" s="12">
+        <f>H87+H88</f>
+        <v/>
+      </c>
+      <c r="I89" s="12">
+        <f>I87+I88</f>
+        <v/>
+      </c>
+      <c r="J89" s="12">
+        <f>J87+J88</f>
+        <v/>
+      </c>
+      <c r="K89" s="12">
+        <f>K87+K88</f>
+        <v/>
+      </c>
+      <c r="L89" s="12">
+        <f>L87+L88</f>
+        <v/>
+      </c>
+      <c r="M89" s="12">
+        <f>M87+M88</f>
+        <v/>
+      </c>
+      <c r="N89" s="12">
+        <f>N87+N88</f>
+        <v/>
+      </c>
+      <c r="O89" s="12">
+        <f>O87+O88</f>
+        <v/>
+      </c>
+      <c r="P89" s="12">
+        <f>P87+P88</f>
+        <v/>
+      </c>
+      <c r="Q89" s="12">
+        <f>Q87+Q88</f>
+        <v/>
+      </c>
+      <c r="R89" s="12">
+        <f>R87+R88</f>
+        <v/>
+      </c>
+      <c r="S89" s="12">
+        <f>S87+S88</f>
+        <v/>
+      </c>
+      <c r="T89" s="12">
+        <f>T87+T88</f>
+        <v/>
+      </c>
+      <c r="U89" s="12">
+        <f>U87+U88</f>
+        <v/>
+      </c>
+      <c r="V89" s="12">
+        <f>V87+V88</f>
+        <v/>
+      </c>
+      <c r="W89" s="12">
+        <f>W87+W88</f>
+        <v/>
+      </c>
+      <c r="X89" s="12">
+        <f>X87+X88</f>
+        <v/>
+      </c>
+      <c r="Y89" s="12">
+        <f>SUM(C89:S89)-T89</f>
         <v/>
       </c>
     </row>
